--- a/output/pdf_financials_xlsx/CBLU.xlsx
+++ b/output/pdf_financials_xlsx/CBLU.xlsx
@@ -4089,16 +4089,16 @@
         <v>0.871855</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>1.081813</v>
+        <v>3.077011</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>4.476158</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>6.253945</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>6.129311</v>
       </c>
       <c r="H92" s="1" t="inlineStr">
         <is>
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>7.401161</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>12.334829</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>12.855907</v>
       </c>
     </row>
     <row r="93">
@@ -7632,7 +7632,11 @@
           <t>Reserves 17</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -10346,7 +10350,11 @@
           <t>Reserves 17</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -12198,7 +12206,11 @@
           <t>Reserves 16</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -13664,7 +13676,11 @@
           <t>Reserves 16</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CBLU.xlsx
+++ b/output/pdf_financials_xlsx/CBLU.xlsx
@@ -859,10 +859,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.016344</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.00254</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -1542,10 +1542,10 @@
         <v>-3.457927</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-8.098566999999999</v>
+        <v>-8.114910999999999</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-5.101918</v>
+        <v>-5.104458</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-3.824219</v>
@@ -1624,10 +1624,10 @@
         <v>-3.457927</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-8.098566999999999</v>
+        <v>-8.114910999999999</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-5.101918</v>
+        <v>-5.104458</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-3.824219</v>
@@ -1665,10 +1665,10 @@
         <v>-150.6189751682521</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-214.2378291381142</v>
+        <v>-214.6701899594093</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-128.4696878932118</v>
+        <v>-128.533646782251</v>
       </c>
       <c r="F30" s="3" t="n">
         <v>-95.03972726353201</v>
@@ -1787,22 +1787,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.496657</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.767116</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.06172</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.507249</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>2.116612</v>
       </c>
       <c r="H34" s="1" t="inlineStr">
         <is>
@@ -1810,13 +1810,13 @@
         </is>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.534451</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.339905</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.15512</v>
       </c>
     </row>
     <row r="35">
@@ -1865,22 +1865,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.496657</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.767116</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.06172</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.507249</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>2.116612</v>
       </c>
       <c r="H36" s="1" t="inlineStr">
         <is>
@@ -1888,13 +1888,13 @@
         </is>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.534451</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.339905</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.15512</v>
       </c>
     </row>
     <row r="37">
@@ -2336,19 +2336,19 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.378261</v>
+        <v>0.8816040000000001</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.520481</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.953794</v>
+        <v>0.892074</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>4.450493</v>
+        <v>0.943244</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.743859</v>
+        <v>0.627247</v>
       </c>
       <c r="H48" s="1" t="inlineStr">
         <is>
@@ -2356,13 +2356,13 @@
         </is>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.826441</v>
+        <v>0.29199</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.141887</v>
+        <v>0.801982</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.918786</v>
+        <v>0.763666</v>
       </c>
     </row>
     <row r="49">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -14076,7 +14076,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -15884,7 +15884,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
@@ -39814,7 +39814,7 @@
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
@@ -41536,7 +41536,7 @@
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E548" t="inlineStr">

--- a/output/pdf_financials_xlsx/CBLU.xlsx
+++ b/output/pdf_financials_xlsx/CBLU.xlsx
@@ -1580,19 +1580,19 @@
         </is>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.013433</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>0.029696</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>0.135641</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.138861</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.146504</v>
       </c>
       <c r="H28" s="1" t="inlineStr">
         <is>
@@ -1600,13 +1600,13 @@
         </is>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.423902</v>
+        <v>0.55676</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.722282</v>
+        <v>0.849193</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.070922</v>
       </c>
     </row>
     <row r="29">
@@ -1621,19 +1621,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.457927</v>
+        <v>-3.444494</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-8.114910999999999</v>
+        <v>-8.085215</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-5.104458</v>
+        <v>-4.968817</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-3.824219</v>
+        <v>-3.685358</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.41138</v>
+        <v>-3.264876</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -1641,13 +1641,13 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-3.469897</v>
+        <v>-3.337039</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-10.303892</v>
+        <v>-10.176981</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-3.886322</v>
+        <v>-3.8154</v>
       </c>
     </row>
     <row r="30">
@@ -1662,19 +1662,19 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-150.6189751682521</v>
+        <v>-150.0338660281705</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-214.6701899594093</v>
+        <v>-213.884618070693</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-128.533646782251</v>
+        <v>-125.1181162042363</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-95.03972726353201</v>
+        <v>-91.58874509762013</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-41.86431166158751</v>
+        <v>-40.06642074481212</v>
       </c>
       <c r="H30" s="1" t="inlineStr">
         <is>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-64.21467287760042</v>
+        <v>-61.75597366861173</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-373.5601884497489</v>
+        <v>-368.9591214862805</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-119.6629393384413</v>
+        <v>-117.47919466063</v>
       </c>
     </row>
     <row r="31">
@@ -4370,19 +4370,19 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.013433</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>0.029696</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>0.135641</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.138861</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.146504</v>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
@@ -4390,13 +4390,13 @@
         </is>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.55676</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.849193</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.070922</v>
       </c>
     </row>
     <row r="101">
@@ -17456,7 +17456,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -17516,7 +17520,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -19818,7 +19822,11 @@
           <t>Additions to intangible assets</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -22478,7 +22486,11 @@
           <t>Depreciation of property and equipment</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -24864,7 +24876,11 @@
           <t>Additions to Intangible Assets</t>
         </is>
       </c>
-      <c r="D293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E293" t="inlineStr">
         <is>
           <t>-</t>
@@ -28158,7 +28174,11 @@
           <t>Depreciation of property and equipment 19,565 8,433</t>
         </is>
       </c>
-      <c r="D343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E343" t="inlineStr">
         <is>
           <t>-</t>
@@ -31346,7 +31366,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -31388,7 +31408,7 @@
         <v>0.423902</v>
       </c>
       <c r="M392" s="5" t="n">
-        <v>-0.722282</v>
+        <v>0.722282</v>
       </c>
       <c r="N392" t="inlineStr">
         <is>
@@ -31412,7 +31432,11 @@
           <t>Depreciation of property and equipment 9</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
@@ -31452,10 +31476,10 @@
         <v>0.132858</v>
       </c>
       <c r="M393" s="5" t="n">
-        <v>-0.126911</v>
+        <v>0.126911</v>
       </c>
       <c r="N393" s="5" t="n">
-        <v>-0.070922</v>
+        <v>0.070922</v>
       </c>
     </row>
     <row r="394">
@@ -38264,7 +38288,11 @@
           <t>Depreciation of property and equipment 8</t>
         </is>
       </c>
-      <c r="D498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E498" t="inlineStr">
         <is>
           <t>-</t>
@@ -39616,7 +39644,11 @@
           <t>Depreciation of property and equipment 10</t>
         </is>
       </c>
-      <c r="D519" t="inlineStr"/>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E519" t="inlineStr">
         <is>
           <t>-</t>
@@ -41800,17 +41832,21 @@
           <t>Depreciation of property and equipment 11</t>
         </is>
       </c>
-      <c r="D552" t="inlineStr"/>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E552" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F552" s="5" t="n">
-        <v>-0.013433</v>
+        <v>0.013433</v>
       </c>
       <c r="G552" s="5" t="n">
-        <v>-0.029696</v>
+        <v>0.029696</v>
       </c>
       <c r="H552" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/CBLU.xlsx
+++ b/output/pdf_financials_xlsx/CBLU.xlsx
@@ -18194,7 +18194,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -19498,7 +19502,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -20802,7 +20810,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -23720,7 +23732,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -25796,7 +25812,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E307" t="inlineStr">
         <is>
           <t>-</t>
@@ -29874,7 +29894,11 @@
           <t>Proceeds intended for private placement</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -30482,7 +30506,11 @@
           <t>Net cash provided by private placement</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E378" s="5" t="n">
         <v>1e-06</v>
       </c>
